--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260803.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260803.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>67.77%</t>
+          <t>66.23%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>5.89%</t>
+          <t>6.47%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.51%</t>
+          <t>3.54%</t>
         </is>
       </c>
     </row>
@@ -682,46 +682,46 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>21,060,286</t>
+          <t>525,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>525,000</t>
+          <t>21,060,286</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
@@ -770,95 +770,95 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>4,864,285</t>
+          <t>578,222</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>578,222</t>
+          <t>4,864,285</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>202608WTEQ6F</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>電子指數期貨</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>187,515</t>
+          <t>110</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>1,241,617</t>
+          <t>187,515</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
@@ -880,112 +880,112 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>202608WTEQ6F</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>電子指數期貨</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1,241,617</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>3,531,000</t>
+          <t>2,059,288</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>2,059,288</t>
+          <t>5,585,296</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>5,585,296</t>
+          <t>3,531,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>328,672</t>
+          <t>173,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>173,000</t>
+          <t>328,672</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1034,46 +1034,46 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>13,495,134</t>
+          <t>899,349</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>899,349</t>
+          <t>145,482</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,83 +1085,83 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>202608WTXQ6F</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>台股指數期貨</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>13,495,134</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1,377,000</t>
+          <t>157,499</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>145,482</t>
+          <t>1,377,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>157,499</t>
+          <t>1,050,822</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>1,050,822</t>
+          <t>620,600</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,39 +1195,39 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>620,600</t>
+          <t>848,897</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>848,897</t>
+          <t>2,061,587</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,061,587</t>
+          <t>142,921</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,44 +1261,44 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>142,921</t>
+          <t>595,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>595,000</t>
+          <t>3,316,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
@@ -1320,68 +1320,68 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>3,316,000</t>
+          <t>1,886,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.22%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>982,659</t>
+          <t>5,888,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,886,000</t>
+          <t>2,724,703</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>5,888,000</t>
+          <t>3,650,981</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,39 +1415,39 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3,650,981</t>
+          <t>982,659</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>807,000</t>
+          <t>152,386</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>2,724,703</t>
+          <t>807,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,39 +1481,39 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>1,446,384</t>
+          <t>4,672,578</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>152,386</t>
+          <t>1,446,384</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>4,672,578</t>
+          <t>46,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>11,120,121</t>
+          <t>7,520,249</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>7,520,249</t>
+          <t>11,120,121</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,83 +1613,83 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>46,000</t>
+          <t>599,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>599,000</t>
+          <t>2,298,107</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>2,298,107</t>
+          <t>1,243,076</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>202608WVHFQ6F</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>1,243,076</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,39 +1701,39 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>202608WVHFQ6F</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>814,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>844,000</t>
+          <t>305,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,39 +1745,39 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>5,203,956</t>
+          <t>844,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>814,000</t>
+          <t>1,636,400</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>305,000</t>
+          <t>188,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>1,636,400</t>
+          <t>98,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,39 +1833,39 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>118,000</t>
+          <t>5,203,956</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>188,000</t>
+          <t>118,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>98,000</t>
+          <t>512,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>238,000</t>
+          <t>401,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>401,000</t>
+          <t>333,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>512,000</t>
+          <t>238,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>333,000</t>
+          <t>179,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>347,000</t>
+          <t>68,538</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>68,538</t>
+          <t>347,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>179,000</t>
+          <t>186,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>186,000</t>
+          <t>164,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>164,000</t>
+          <t>713,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>713,000</t>
+          <t>266,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,22 +2163,22 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>266,000</t>
+          <t>75,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
@@ -2207,17 +2207,17 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>75,000</t>
+          <t>120,000</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -2229,39 +2229,35 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>120,000</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>0.02%</t>
-        </is>
-      </c>
+          <t>3,597,368,563</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>3,604,061,786</t>
+          <t>308,614,669</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr"/>
@@ -2269,17 +2265,17 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>PFUR_NTD</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>PAYABLES FOR UNITS REDEEMED</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>320,279,242</t>
+          <t>295,907,810</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr"/>
@@ -2297,7 +2293,7 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>-2,451,835,064</t>
+          <t>-2,398,603,470</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr"/>
